--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -685,14 +685,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -709,13 +708,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -753,12 +753,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">30226
 </t>
         </is>
       </c>
@@ -770,7 +771,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -782,13 +783,14 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -805,7 +807,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -832,7 +834,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -844,7 +846,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -856,7 +858,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -874,7 +876,8 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -891,8 +894,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -903,19 +905,19 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -933,19 +935,18 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>616</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -962,8 +963,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4316
 </t>
         </is>
       </c>
@@ -1013,13 +1013,13 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1029,12 +1029,16 @@
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
-        <v/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">606
+</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1045,7 +1049,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1063,7 +1067,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1117,12 +1121,12 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1155,12 +1159,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1172,8 +1176,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1190,31 +1193,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1502
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">173
 </t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1173
-</t>
-        </is>
-      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1226,7 +1229,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3189
 </t>
         </is>
       </c>
@@ -1244,7 +1247,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1256,30 +1259,30 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -1300,26 +1303,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1330,13 +1329,13 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1347,8 +1346,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1359,7 +1357,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18656
 </t>
         </is>
       </c>
@@ -1371,13 +1369,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1407,7 +1405,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1419,25 +1417,25 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1457,42 +1455,39 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1503,19 +1498,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1533,7 +1526,8 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1549,7 +1543,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1572,18 +1567,19 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1610,8 +1606,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1622,7 +1617,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1633,14 +1628,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1651,12 +1644,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5447
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1666,13 +1661,13 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1690,8 +1685,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1702,31 +1696,29 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1738,7 +1730,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">8065
 </t>
         </is>
       </c>
@@ -1765,19 +1757,18 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450
+          <t xml:space="preserve">4456
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -1801,13 +1792,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1828,8 +1819,11 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
-        <v/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -1851,7 +1845,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1863,7 +1857,8 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1886,13 +1881,13 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -1931,8 +1926,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1943,8 +1937,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1985,7 +1978,8 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1996,19 +1990,19 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -2026,19 +2020,17 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -2056,7 +2048,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -2077,8 +2069,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
-</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2107,7 +2098,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2125,7 +2116,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -2143,14 +2134,13 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2161,7 +2151,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">4286
 </t>
         </is>
       </c>
@@ -2173,7 +2163,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">3247
 </t>
         </is>
       </c>
@@ -2191,14 +2181,13 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2209,8 +2198,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2236,7 +2224,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
@@ -2248,7 +2236,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2260,13 +2248,13 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2284,25 +2272,25 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2326,13 +2314,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2368,7 +2356,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2400,20 +2388,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2442,25 +2427,24 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2508,7 +2492,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2520,19 +2504,18 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2553,19 +2536,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -2607,28 +2590,31 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1609
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9186
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211222
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2639,12 +2625,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t xml:space="preserve">425
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2655,8 +2643,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2667,23 +2654,24 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>464</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2704,7 +2692,9 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t xml:space="preserve">1
+3986
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2721,32 +2711,28 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2766,7 +2752,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2790,51 +2776,56 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2428
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2853,35 +2844,36 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373
+          <t xml:space="preserve">432
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2892,13 +2884,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2910,7 +2901,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2922,13 +2913,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2429
 </t>
         </is>
       </c>
@@ -2940,7 +2931,8 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2951,12 +2943,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>044</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2979,13 +2972,14 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">46
+8 179
 </t>
         </is>
       </c>
@@ -3030,20 +3024,19 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3054,8 +3047,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3066,13 +3058,13 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -3096,7 +3088,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3120,8 +3112,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3132,18 +3123,21 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">212
+44
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">62
+818
 </t>
         </is>
       </c>
@@ -3164,40 +3158,42 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">3
+1 8 4
+7
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3209,13 +3205,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -3233,20 +3228,17 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3263,14 +3255,12 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3281,20 +3271,18 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="Z20" s="3" t="n">
@@ -3323,8 +3311,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3339,14 +3326,12 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G21" s="3" t="n">
+        <v/>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3364,7 +3349,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3376,7 +3361,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3405,19 +3391,19 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">5310
 </t>
         </is>
       </c>
@@ -3429,23 +3415,25 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t xml:space="preserve">259
+8111
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3471,25 +3459,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3500,7 +3487,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -3524,7 +3511,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3536,13 +3523,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8720
 </t>
         </is>
       </c>
@@ -3572,8 +3559,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3584,25 +3570,24 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3629,138 +3614,139 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
-</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8826
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4382
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29526
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1469
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3781,139 +3767,139 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
-</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
+          <t xml:space="preserve">8724
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3934,142 +3920,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">3261
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>814</t>
+          <t xml:space="preserve">748
+</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4089,52 +4075,53 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">3261
+</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>363</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4146,13 +4133,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
@@ -4164,19 +4150,19 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -4187,8 +4173,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -4199,7 +4184,8 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -4210,8 +4196,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -4222,7 +4207,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4243,8 +4228,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4261,19 +4245,19 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -4285,7 +4269,8 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -4302,7 +4287,8 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -4313,19 +4299,19 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4343,25 +4329,24 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -4379,7 +4364,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">16
+54
 </t>
         </is>
       </c>
@@ -4400,17 +4386,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4421,24 +4409,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4450,31 +4439,30 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4492,48 +4480,47 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>081</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4559,14 +4546,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4583,58 +4568,58 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12396
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -4661,35 +4646,36 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4709,88 +4695,83 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -4817,13 +4798,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>855</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4840,13 +4821,13 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4867,13 +4848,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4891,31 +4871,31 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4926,54 +4906,52 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4997,13 +4975,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5024,19 +5002,19 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">4373
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5048,7 +5026,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5060,33 +5038,37 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -5097,13 +5079,13 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -5121,19 +5103,19 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -5144,19 +5126,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2
+78
 </t>
         </is>
       </c>
@@ -5177,13 +5159,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">32720
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -5195,12 +5177,14 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -5211,110 +5195,100 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5334,8 +5308,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5351,7 +5324,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5363,19 +5336,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5393,82 +5366,84 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">832
+</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">54
+5
 </t>
         </is>
       </c>
@@ -5489,144 +5464,138 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
-</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v/>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">31
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2216
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">6
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5646,144 +5615,141 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">3989
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2890
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v/>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">3266
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5804,36 +5770,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
+          <t xml:space="preserve">16835
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t xml:space="preserve">561
+</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5845,102 +5812,98 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">1035
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">4325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>836</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -5961,139 +5924,141 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
+          <t xml:space="preserve">3367
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">3600
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0029</t>
+          <t xml:space="preserve">2646
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>551</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13996
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">2526
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6114,91 +6079,85 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
-</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9251
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6210,49 +6169,46 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6272,142 +6228,144 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2024
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6427,142 +6385,143 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>0401</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">584
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6582,144 +6541,144 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488
+          <t xml:space="preserve">442
+2 6
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6739,126 +6698,120 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">3413
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1781
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>611</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6868,13 +6821,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6894,79 +6847,77 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6978,59 +6929,60 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">7335
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -7049,133 +7001,143 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1416
-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v/>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">777
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18256
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t xml:space="preserve">2424
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">6 7
+57
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7196,23 +7158,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">2480
+</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7223,46 +7187,50 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>0564</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18256
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">20 8
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -7279,15 +7247,12 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v/>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -7303,28 +7268,29 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
+          <t xml:space="preserve">2424
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v/>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -679,36 +679,34 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">94375
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -720,7 +718,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -735,50 +733,49 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30226
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -789,8 +786,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -799,23 +795,14 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
+      <c r="X4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v/>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -832,51 +819,45 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v/>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v/>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -894,30 +875,28 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
+          <t xml:space="preserve">1900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v/>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -929,46 +908,46 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v/>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t xml:space="preserve">741
+</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -989,13 +968,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4316
-</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1013,43 +991,40 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v/>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -1061,37 +1036,36 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">12329
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">16089
 </t>
         </is>
       </c>
@@ -1103,30 +1077,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1147,77 +1122,73 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">14373
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">2330
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
-</t>
-        </is>
-      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1673
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
@@ -1229,7 +1200,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1241,13 +1212,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">20221
 </t>
         </is>
       </c>
@@ -1259,30 +1230,31 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1276
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1303,22 +1275,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12972
+</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>526</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t xml:space="preserve">1262
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1329,13 +1305,14 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1346,66 +1323,66 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18656
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1423,19 +1400,20 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1455,40 +1433,35 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">16665
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
+          <t xml:space="preserve">8526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v/>
       </c>
       <c r="F9" s="3" t="n">
         <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v/>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1498,58 +1471,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">443
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">1943
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">1963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
+          <t xml:space="preserve">14409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1629
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">16173
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">13609
 </t>
         </is>
       </c>
@@ -1561,31 +1537,22 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+          <t xml:space="preserve">11261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v/>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1606,18 +1573,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t xml:space="preserve">3333
+</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3051
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1628,12 +1596,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1161
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1644,36 +1614,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5447
-</t>
-        </is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t xml:space="preserve">1876
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v/>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -1685,40 +1650,42 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1264
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1730,13 +1697,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8065
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1757,30 +1724,31 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456
+          <t xml:space="preserve">14450
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1792,12 +1760,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1807,11 +1776,8 @@
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
+      <c r="L11" s="3" t="n">
+        <v/>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1821,26 +1787,25 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1851,7 +1816,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">19819
 </t>
         </is>
       </c>
@@ -1863,19 +1828,19 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -1887,15 +1852,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v/>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1926,18 +1888,20 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1948,7 +1912,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1960,14 +1924,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1990,13 +1953,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
@@ -2014,41 +1977,42 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>533</t>
+          <t xml:space="preserve">53
+</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1247
+</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2069,12 +2033,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t xml:space="preserve">393567
+</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -2098,31 +2063,31 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
@@ -2140,18 +2105,16 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v/>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2163,7 +2126,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3247
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -2175,35 +2138,37 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1238
+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1977
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2224,19 +2189,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">139740
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1325
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2248,43 +2213,40 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v/>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2296,7 +2258,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
@@ -2314,13 +2276,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2350,13 +2312,14 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1930
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2388,28 +2351,31 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">1249
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -2421,19 +2387,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2442,15 +2407,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
+      <c r="N15" s="3" t="n">
+        <v/>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2474,13 +2436,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">1638
 </t>
         </is>
       </c>
@@ -2492,30 +2454,31 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">12411
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -2536,19 +2499,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">119928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2560,21 +2523,18 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v/>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -2584,13 +2544,13 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
@@ -2602,48 +2562,49 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211222
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">11428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
+          <t xml:space="preserve">13687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5334415</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2652,26 +2613,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
+      <c r="W16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v/>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">14551
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2692,9 +2648,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-3986
-</t>
+          <t>399</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2711,7 +2665,8 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">12249
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2721,18 +2676,20 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2740,25 +2697,25 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2770,36 +2727,36 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1106
+</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -2811,19 +2768,19 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2844,7 +2801,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -2856,40 +2813,40 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v/>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1871
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2913,19 +2870,19 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2937,30 +2894,31 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>631</t>
+          <t xml:space="preserve">1631
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2256
 </t>
         </is>
       </c>
@@ -2972,14 +2930,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-8 179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3000,7 +2957,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4239
+          <t xml:space="preserve">14239
 </t>
         </is>
       </c>
@@ -3018,36 +2975,38 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">11248
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3058,25 +3017,24 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3100,8 +3058,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3112,7 +3069,8 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1258
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3123,21 +3081,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-44
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-818
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3158,42 +3114,43 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-1 8 4
-7
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3205,45 +3162,49 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">124080
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3255,12 +3216,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t xml:space="preserve">707
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3271,22 +3234,27 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">1205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -3305,13 +3273,14 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">14335
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">1308
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3326,18 +3295,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
-        <v/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3347,11 +3319,8 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
+      <c r="K21" s="3" t="n">
+        <v/>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -3361,8 +3330,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3373,37 +3341,34 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v/>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -3415,30 +3380,30 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
-8111
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3459,24 +3424,26 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">374 0
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3487,19 +3454,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3511,7 +3478,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3523,19 +3490,19 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3553,13 +3520,14 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">1564
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3570,24 +3538,25 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -3614,28 +3583,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t xml:space="preserve">19255
+</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t xml:space="preserve">1531
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">928
+</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>603</t>
+          <t xml:space="preserve">1603
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3652,101 +3625,91 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1355
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826
+          <t xml:space="preserve">18828
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382
+          <t xml:space="preserve">14372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v/>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29526
+          <t xml:space="preserve">12952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v/>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">11267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14110
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -3767,7 +3730,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t xml:space="preserve">3851
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3784,18 +3748,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -3822,31 +3787,28 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v/>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3864,19 +3826,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">1590
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
@@ -3888,19 +3850,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3920,31 +3882,31 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">13740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1257
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3961,15 +3923,12 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v/>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3979,13 +3938,13 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -3997,64 +3956,66 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">1313
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">9569
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">12242
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">17476
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4075,139 +4036,142 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1246
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4228,145 +4192,142 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v/>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">7208
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4386,140 +4347,145 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t xml:space="preserve">93893
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1398
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>081</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4540,59 +4506,61 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
+          <t xml:space="preserve">4085
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12396
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -4604,25 +4572,25 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -4634,47 +4602,49 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4695,139 +4665,145 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t xml:space="preserve">18564
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t xml:space="preserve">1503
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1919
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">14419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">11385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">11137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">13328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">18231
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">11243
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">13998
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4848,140 +4824,138 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>064</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t xml:space="preserve">1666
+</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -5008,137 +4982,131 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v/>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
+          <t xml:space="preserve">1884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v/>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">691
+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-78
+          <t xml:space="preserve">11188
 </t>
         </is>
       </c>
@@ -5159,136 +5127,139 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32720
+          <t xml:space="preserve">13970
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v/>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>816</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>495</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t xml:space="preserve">874
+</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1329
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">19477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1261
+</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5308,85 +5279,83 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">3624
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">1873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v/>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
@@ -5396,13 +5365,13 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -5414,36 +5383,36 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0554</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-5
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5464,30 +5433,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t xml:space="preserve">1879
+</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -5496,24 +5467,28 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="3" t="n">
-        <v/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>241</t>
+          <t xml:space="preserve">2010
+</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5524,24 +5499,24 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">2093
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5553,7 +5528,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -5571,7 +5546,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5583,18 +5558,19 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5621,24 +5597,25 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5662,7 +5639,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5680,13 +5657,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -5698,19 +5675,19 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25938
 </t>
         </is>
       </c>
@@ -5728,28 +5705,31 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2050
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5770,27 +5750,18 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
-</t>
-        </is>
+          <t xml:space="preserve">116835
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v/>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -5800,7 +5771,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5818,7 +5789,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
@@ -5828,53 +5799,51 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
+      <c r="M37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v/>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4325
+          <t xml:space="preserve">14325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t xml:space="preserve">1657
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5883,27 +5852,21 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
+      <c r="W37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v/>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">3966
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">3424
 </t>
         </is>
       </c>
@@ -5930,20 +5893,19 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5954,27 +5916,23 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
+          <t xml:space="preserve">12111
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5984,30 +5942,31 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -6019,46 +5978,49 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2526
-</t>
-        </is>
-      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6079,7 +6041,8 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t xml:space="preserve">14008
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6090,74 +6053,79 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1205
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
@@ -6169,13 +6137,13 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6186,29 +6154,32 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>768</t>
+          <t xml:space="preserve">1268
+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6228,19 +6199,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -6252,31 +6223,30 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -6294,25 +6264,25 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -6330,7 +6300,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
@@ -6348,24 +6318,26 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6385,7 +6357,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">14488
 </t>
         </is>
       </c>
@@ -6397,31 +6369,32 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6432,12 +6405,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0401</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -6449,7 +6423,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6473,7 +6447,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -6485,8 +6459,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6497,30 +6470,30 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6541,144 +6514,143 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-2 6
-</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">19249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>028</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6698,23 +6670,26 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">1320
+</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">1886
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6725,108 +6700,115 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27914
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1828
+</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
@@ -6853,19 +6835,19 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6882,7 +6864,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6894,97 +6876,87 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2286
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7335
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
-</t>
-        </is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v/>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -7001,47 +6973,36 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168711
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v/>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -7053,91 +7014,79 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18256
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v/>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">102342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16912
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">40844
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v/>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1848324382
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -7158,12 +7107,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">3117
+</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -7175,7 +7125,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -7187,7 +7137,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -7199,15 +7149,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7217,13 +7164,13 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18256
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 8
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -7241,22 +7188,25 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -7268,31 +7218,30 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2242
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v/>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -679,34 +679,37 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94375
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">9124 11
 </t>
         </is>
       </c>
@@ -718,12 +721,15 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 8
+</t>
+        </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -733,25 +739,25 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">11785
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -763,19 +769,20 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t xml:space="preserve">637
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -786,7 +793,8 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">277
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -819,12 +827,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -836,7 +846,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -848,22 +858,19 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
         <v/>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
+      <c r="J5" s="3" t="n">
+        <v/>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -881,18 +888,21 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -908,19 +918,19 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -930,18 +940,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="3" t="n">
-        <v/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">7261
 </t>
         </is>
       </c>
@@ -968,12 +981,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t xml:space="preserve">8316
+</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -997,34 +1011,37 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1036,54 +1053,55 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12329
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16089
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -1095,13 +1113,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1122,133 +1140,136 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14373
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 82
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="n">
         <v/>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1673
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1876
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20221
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1276
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779
+          <t xml:space="preserve">17729
 </t>
         </is>
       </c>
@@ -1275,7 +1296,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12972
+          <t xml:space="preserve">989716
 </t>
         </is>
       </c>
@@ -1287,13 +1308,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -1311,7 +1332,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1323,13 +1344,13 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1341,43 +1362,44 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t xml:space="preserve">954
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1400,7 +1422,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -1410,11 +1432,8 @@
 </t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+      <c r="Z8" s="3" t="n">
+        <v/>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1433,25 +1452,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1460,8 +1486,11 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
-        <v/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2112
+</t>
+        </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1471,61 +1500,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14409
+          <t xml:space="preserve">18409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
+          <t xml:space="preserve">12173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">18319
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13609
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
@@ -1537,22 +1566,28 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
       </c>
       <c r="X9" s="3" t="n">
         <v/>
       </c>
-      <c r="Y9" s="3" t="n">
-        <v/>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114184
+</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -1573,19 +1608,20 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3051
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1602,13 +1638,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1618,12 +1654,15 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1633,12 +1672,15 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n">
-        <v/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -1656,19 +1698,19 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
@@ -1680,7 +1722,8 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1691,13 +1734,13 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">8259
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
@@ -1724,7 +1767,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14450
+          <t xml:space="preserve">14451
 </t>
         </is>
       </c>
@@ -1742,7 +1785,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1760,24 +1803,27 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1787,77 +1833,80 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">2467
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">23 08
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1876,13 +1925,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3836
-</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1894,25 +1942,25 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1924,13 +1972,14 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1953,13 +2002,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1977,7 +2026,8 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1988,19 +2038,19 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -2012,7 +2062,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2033,13 +2083,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">393567
+          <t xml:space="preserve">0856
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -2063,7 +2113,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2075,19 +2125,19 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -2105,16 +2155,19 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2138,19 +2191,19 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2162,13 +2215,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2189,13 +2242,13 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139740
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325
+          <t xml:space="preserve">2325
 </t>
         </is>
       </c>
@@ -2219,18 +2272,21 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -2240,13 +2296,13 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2258,14 +2314,13 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2282,7 +2337,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2345,7 +2400,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">16433
 </t>
         </is>
       </c>
@@ -2357,13 +2412,13 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2375,24 +2430,25 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2404,15 +2460,19 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2436,13 +2496,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
@@ -2454,13 +2514,13 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2472,7 +2532,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">17410
 </t>
         </is>
       </c>
@@ -2499,37 +2559,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119928
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">11299
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9918
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2550,43 +2610,42 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
-</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">10559
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
+          <t xml:space="preserve">44641
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
@@ -2598,13 +2657,14 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13687
+          <t xml:space="preserve">3687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334415</t>
+          <t xml:space="preserve">531
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2613,15 +2673,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v/>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1375
+</t>
+        </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14551
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
@@ -2648,12 +2714,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -2665,14 +2731,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12249
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v/>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -2682,7 +2746,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2695,27 +2759,24 @@
       <c r="K17" s="3" t="n">
         <v/>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v/>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2727,13 +2788,14 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t xml:space="preserve">1820
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2744,7 +2806,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2756,7 +2818,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">2482
 </t>
         </is>
       </c>
@@ -2801,46 +2863,45 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
         <v/>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1871
-</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2852,37 +2913,36 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2894,13 +2954,13 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2918,13 +2978,13 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">4113
 </t>
         </is>
       </c>
@@ -2957,13 +3017,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14239
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">9225
 </t>
         </is>
       </c>
@@ -2975,19 +3034,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11248
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2999,13 +3058,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
@@ -3017,7 +3075,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -3029,36 +3087,38 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">875
+</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2618
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">12953
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">540
+</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3069,7 +3129,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">16558
 </t>
         </is>
       </c>
@@ -3081,21 +3141,18 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v/>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -3114,13 +3171,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">8568
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
@@ -3132,7 +3189,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -3144,7 +3201,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3156,31 +3213,28 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124080
-</t>
-        </is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v/>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3198,19 +3252,19 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3222,7 +3276,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">95 1
 </t>
         </is>
       </c>
@@ -3234,7 +3288,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3246,7 +3300,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
@@ -3273,13 +3327,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14335
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -3303,13 +3357,13 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3319,8 +3373,11 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
-        <v/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -3330,7 +3387,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3341,16 +3399,19 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -3368,7 +3429,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3380,13 +3441,14 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
@@ -3424,8 +3486,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 0
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3434,11 +3495,8 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v/>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3448,25 +3506,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3496,73 +3554,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1216
 </t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1564
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1216
-</t>
-        </is>
-      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3595,19 +3653,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">160274
 </t>
         </is>
       </c>
@@ -3625,51 +3683,57 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18828
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14372
+          <t xml:space="preserve">11372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">15357
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11451
+</t>
+        </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
@@ -3679,7 +3743,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12952
+          <t xml:space="preserve">2952
 </t>
         </is>
       </c>
@@ -3689,21 +3753,27 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v/>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107
+</t>
+        </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11267
+          <t xml:space="preserve">2267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">18110
 </t>
         </is>
       </c>
@@ -3730,13 +3800,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -3748,19 +3818,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -3772,97 +3842,101 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="n">
         <v/>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1590
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1244
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1253
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3882,36 +3956,37 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13740
+          <t xml:space="preserve">3740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3923,12 +3998,15 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81414 6
+</t>
+        </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3944,7 +4022,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -3956,30 +4034,31 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">1040
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9569
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
@@ -3991,13 +4070,13 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4009,13 +4088,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17476
+          <t xml:space="preserve">1748
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -4036,7 +4115,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -4048,8 +4127,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4066,13 +4144,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4084,7 +4162,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -4096,24 +4174,25 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4137,37 +4216,36 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v/>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -4192,7 +4270,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9522
 </t>
         </is>
       </c>
@@ -4204,13 +4282,13 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4226,12 +4304,15 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n">
-        <v/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4243,7 +4324,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4255,31 +4336,31 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4291,31 +4372,30 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2098
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4327,7 +4407,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4347,7 +4428,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93893
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -4359,8 +4440,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4377,25 +4457,25 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4413,19 +4493,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">82813
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4437,7 +4517,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4449,26 +4529,25 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4479,7 +4558,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4506,7 +4585,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
@@ -4518,52 +4597,51 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8229
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
@@ -4572,7 +4650,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4584,13 +4662,13 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4602,7 +4680,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4620,7 +4698,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4632,13 +4710,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81828
 </t>
         </is>
       </c>
@@ -4665,37 +4743,37 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
+          <t xml:space="preserve">118364
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4713,13 +4791,13 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4731,55 +4809,55 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">91034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14419
+          <t xml:space="preserve">142419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13328
+          <t xml:space="preserve">3328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18231
+          <t xml:space="preserve">11231
 </t>
         </is>
       </c>
@@ -4791,14 +4869,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11243
-</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13998
-</t>
+          <t>394</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4824,12 +4900,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4841,18 +4917,20 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">105
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t xml:space="preserve">11824
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4867,97 +4945,96 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="n">
         <v/>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>064</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1245
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1666
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1220
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">949
-</t>
-        </is>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -4976,51 +5053,55 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">9437
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5032,24 +5113,27 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">4215
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
@@ -5059,7 +5143,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5071,24 +5155,25 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">5606
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">2682
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11288
 </t>
         </is>
       </c>
@@ -5100,13 +5185,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11188
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5127,50 +5212,54 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13970
+          <t xml:space="preserve">3971
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
@@ -5182,12 +5271,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5205,42 +5295,43 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19477
+          <t xml:space="preserve">477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5252,7 +5343,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5279,13 +5370,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5303,19 +5394,19 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5327,7 +5418,8 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1024
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5350,12 +5442,15 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
@@ -5365,31 +5460,32 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">78868
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>0554</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -5400,19 +5496,19 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">18328
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5439,55 +5535,55 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5499,24 +5595,25 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t xml:space="preserve">834
+</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5528,7 +5625,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -5540,25 +5637,25 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -5570,7 +5667,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5597,19 +5694,18 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">9243
 </t>
         </is>
       </c>
@@ -5633,13 +5729,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5657,13 +5753,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5675,25 +5771,25 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25938
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
@@ -5705,7 +5801,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050
+          <t xml:space="preserve">2958
 </t>
         </is>
       </c>
@@ -5717,21 +5813,18 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">8468
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v/>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5754,14 +5847,23 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14501
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1255
+</t>
+        </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -5771,7 +5873,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">92241
 </t>
         </is>
       </c>
@@ -5789,7 +5891,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5799,15 +5901,21 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13965
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14325
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -5819,7 +5927,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5831,18 +5939,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t xml:space="preserve">3437
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
@@ -5852,11 +5961,17 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v/>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
@@ -5866,7 +5981,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -5905,7 +6020,8 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5916,23 +6032,27 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5942,25 +6062,25 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19 3
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5978,19 +6098,19 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
@@ -6002,7 +6122,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2 24 2
 </t>
         </is>
       </c>
@@ -6014,13 +6134,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -6041,19 +6161,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">140018
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">4118
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -6065,7 +6185,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -6075,27 +6195,24 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
+      <c r="I39" s="3" t="n">
+        <v/>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -6107,7 +6224,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6119,19 +6236,19 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -6143,7 +6260,8 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t xml:space="preserve">5345
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6154,31 +6272,31 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">1754
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6205,13 +6323,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>94446</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -6223,30 +6340,31 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6264,7 +6382,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6276,13 +6394,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6300,7 +6418,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6312,31 +6430,31 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12172
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6357,14 +6475,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14488
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6387,31 +6504,31 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6447,7 +6564,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6459,7 +6576,8 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t xml:space="preserve">584
+</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6470,7 +6588,8 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6481,7 +6600,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6514,12 +6633,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -6531,13 +6651,13 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6549,30 +6669,31 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>028</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6584,7 +6705,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6608,19 +6729,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">2282
 </t>
         </is>
       </c>
@@ -6632,24 +6753,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1104
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">187080
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6670,19 +6792,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6700,19 +6822,19 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6748,19 +6870,19 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6772,32 +6894,28 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v/>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27914
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6808,7 +6926,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6829,25 +6947,26 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6864,7 +6983,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
@@ -6888,17 +7007,20 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">2008
+</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6909,13 +7031,13 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6927,19 +7049,19 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">18223
 </t>
         </is>
       </c>
@@ -6975,106 +7097,127 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168711
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">188411
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8411
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1056
+</t>
+        </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">28161
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">121804
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
         <v/>
       </c>
-      <c r="N45" s="3" t="n">
-        <v/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101092106191
+</t>
+        </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102342
+          <t xml:space="preserve">02041
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
+          <t xml:space="preserve">168084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16912
+          <t xml:space="preserve">12572
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">12917
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">183179
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40844
+          <t xml:space="preserve">448414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="n">
         <v/>
       </c>
-      <c r="W45" s="3" t="n">
-        <v/>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11222
+</t>
+        </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848324382
+          <t xml:space="preserve">9247
 </t>
         </is>
       </c>
@@ -7107,13 +7250,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">5117
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -7125,120 +7268,119 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11226
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9247
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v/>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2062
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1690
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2242
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
       </c>
       <c r="Z46" s="3" t="n">
         <v/>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -697,7 +697,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124 11
+          <t xml:space="preserve">91124 1
 </t>
         </is>
       </c>
@@ -727,13 +727,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8
+          <t xml:space="preserve">8 8 8
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
@@ -745,7 +745,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11785
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -793,7 +793,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -846,7 +846,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -868,11 +868,8 @@
       <c r="J5" s="3" t="n">
         <v/>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
+      <c r="K5" s="3" t="n">
+        <v/>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -888,7 +885,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -898,11 +895,8 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
+      <c r="P5" s="3" t="n">
+        <v/>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -930,7 +924,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -942,19 +936,19 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7261
+          <t xml:space="preserve">741
 </t>
         </is>
       </c>
@@ -981,7 +975,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316
+          <t xml:space="preserve">4326
 </t>
         </is>
       </c>
@@ -1011,25 +1005,25 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1083,13 +1077,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1140,19 +1134,19 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1164,19 +1158,19 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1194,25 +1188,25 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">2620
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -1269,7 +1263,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17729
+          <t xml:space="preserve">7279
 </t>
         </is>
       </c>
@@ -1296,7 +1290,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989716
+          <t xml:space="preserve">297 6
 </t>
         </is>
       </c>
@@ -1308,28 +1302,28 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1356,7 +1350,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1458,13 +1452,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11526
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1488,7 +1482,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -1524,7 +1518,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409
+          <t xml:space="preserve">4409
 </t>
         </is>
       </c>
@@ -1542,13 +1536,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18319
+          <t xml:space="preserve">12319
 </t>
         </is>
       </c>
@@ -1576,18 +1570,21 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="3" t="n">
-        <v/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114184
+          <t xml:space="preserve">1141024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -1638,27 +1635,21 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v/>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1674,13 +1665,13 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">2193
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -1734,7 +1725,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1746,7 +1737,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1767,7 +1758,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14451
+          <t xml:space="preserve">24451
 </t>
         </is>
       </c>
@@ -1797,7 +1788,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1809,13 +1800,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1833,7 +1824,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2467
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -1845,7 +1836,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1857,7 +1848,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 08
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1869,13 +1860,13 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">587
 </t>
         </is>
       </c>
@@ -1887,7 +1878,8 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">247 16
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1925,12 +1917,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1954,7 +1946,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1972,7 +1964,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2056,13 +2048,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2083,7 +2075,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2101,7 +2093,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2355
 </t>
         </is>
       </c>
@@ -2125,13 +2117,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2209,13 +2201,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -2248,7 +2240,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2272,7 +2264,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2282,11 +2274,8 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+      <c r="J14" s="3" t="n">
+        <v/>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -2302,7 +2291,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2320,7 +2309,8 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2337,7 +2327,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2367,13 +2357,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2400,7 +2390,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16433
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
@@ -2412,7 +2402,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2424,19 +2414,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2448,7 +2438,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">16 8
 </t>
         </is>
       </c>
@@ -2508,7 +2498,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -2532,7 +2522,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17410
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2565,19 +2555,19 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11299
+          <t xml:space="preserve">192499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9918
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2593,8 +2583,11 @@
 </t>
         </is>
       </c>
-      <c r="I16" s="3" t="n">
-        <v/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -2610,30 +2603,30 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
+          <t xml:space="preserve">9246
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10559
+          <t xml:space="preserve">1058
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44641
+          <t xml:space="preserve">4448
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2645,7 +2638,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2714,12 +2707,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">398
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2735,8 +2729,11 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
-        <v/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -2746,21 +2743,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
         <v/>
       </c>
-      <c r="L17" s="3" t="n">
-        <v/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -2776,7 +2774,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2794,7 +2792,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">282240
 </t>
         </is>
       </c>
@@ -2806,25 +2804,25 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2482
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2836,13 +2834,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2863,7 +2861,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2875,45 +2873,47 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1713
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2930,13 +2930,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2972,19 +2972,19 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2506
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4113
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9225
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3058,7 +3058,8 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -3099,19 +3100,19 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2618
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12953
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3129,7 +3130,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16558
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -3147,7 +3148,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -3171,13 +3172,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568
+          <t xml:space="preserve">9568
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3189,7 +3190,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3201,7 +3202,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3211,15 +3212,14 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v/>
       </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3240,19 +3240,19 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3264,13 +3264,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
@@ -3288,8 +3288,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3375,7 +3374,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3435,7 +3434,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2089
 </t>
         </is>
       </c>
@@ -3459,7 +3458,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">8508
 </t>
         </is>
       </c>
@@ -3486,7 +3485,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>344</t>
+          <t xml:space="preserve">3741
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3495,8 +3495,10 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
-        <v/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3506,7 +3508,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
@@ -3518,7 +3520,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3596,19 +3598,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1935
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3620,7 +3622,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3647,13 +3649,13 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3665,7 +3667,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160274
+          <t xml:space="preserve">6059
 </t>
         </is>
       </c>
@@ -3689,7 +3691,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">4953
 </t>
         </is>
       </c>
@@ -3713,25 +3715,25 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11372
+          <t xml:space="preserve">4372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15357
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11451
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
@@ -3755,13 +3757,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3773,7 +3775,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -3800,25 +3802,25 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -3830,7 +3832,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3842,7 +3844,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3866,7 +3868,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3878,13 +3880,13 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3896,7 +3898,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23 8
 </t>
         </is>
       </c>
@@ -3962,19 +3964,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -3986,40 +3988,40 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 6
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81414 6
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4028,25 +4030,25 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">31 5
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4058,19 +4060,19 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4082,7 +4084,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4094,7 +4096,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4156,7 +4158,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -4180,7 +4182,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">89 2
 </t>
         </is>
       </c>
@@ -4210,7 +4212,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4222,7 +4224,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4270,25 +4272,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522
+          <t xml:space="preserve">3548
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4300,13 +4301,13 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4342,7 +4343,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -4360,7 +4361,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4378,18 +4379,18 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>634</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4401,7 +4402,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4428,7 +4429,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4440,7 +4441,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4451,19 +4453,19 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4493,7 +4495,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82813
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4505,7 +4507,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4535,7 +4537,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4547,18 +4549,18 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4585,30 +4587,29 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8229
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4650,7 +4651,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4662,7 +4663,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4680,13 +4681,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">2245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4710,19 +4711,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81828
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4743,7 +4744,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118364
+          <t xml:space="preserve">118564
 </t>
         </is>
       </c>
@@ -4755,13 +4756,13 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -4779,7 +4780,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4797,7 +4798,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">9296
 </t>
         </is>
       </c>
@@ -4809,25 +4810,25 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91034
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142419
+          <t xml:space="preserve">4419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">2385
 </t>
         </is>
       </c>
@@ -4851,13 +4852,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4869,12 +4870,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>613</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>439</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4900,19 +4901,18 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>096</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4945,15 +4945,12 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4971,12 +4968,13 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4994,7 +4992,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -5005,13 +5004,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">28246
 </t>
         </is>
       </c>
@@ -5023,13 +5022,13 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5053,13 +5052,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">4128
 </t>
         </is>
       </c>
@@ -5071,7 +5070,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -5089,7 +5088,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5101,85 +5100,85 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4215
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5606
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -5191,7 +5190,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -5212,13 +5211,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3971
-</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5230,7 +5228,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5242,14 +5240,13 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5259,7 +5256,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5301,7 +5298,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2389
 </t>
         </is>
       </c>
@@ -5343,13 +5340,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">17276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5376,7 +5373,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -5394,7 +5391,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5418,7 +5415,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5460,7 +5457,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5472,19 +5469,19 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78868
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5496,13 +5493,13 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18328
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5529,7 +5526,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5595,13 +5592,13 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5637,19 +5634,19 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5661,13 +5658,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5700,24 +5697,24 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19 0 1
 </t>
         </is>
       </c>
@@ -5735,7 +5732,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -5753,7 +5750,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5789,7 +5786,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -5801,19 +5798,19 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2958
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8468
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5849,19 +5846,19 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14501
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5873,7 +5870,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92241
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5903,13 +5900,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5927,7 +5924,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1396
 </t>
         </is>
       </c>
@@ -5939,7 +5936,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">12560
 </t>
         </is>
       </c>
@@ -6032,7 +6029,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -6044,13 +6041,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6098,7 +6094,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6110,7 +6106,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -6122,7 +6118,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 24 2
+          <t xml:space="preserve">224 1
 </t>
         </is>
       </c>
@@ -6134,7 +6130,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
@@ -6161,13 +6157,13 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140018
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4118
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -6185,13 +6181,13 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1585
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -6200,7 +6196,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6212,7 +6208,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6224,7 +6220,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2884
 </t>
         </is>
       </c>
@@ -6236,31 +6232,31 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5345
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6284,19 +6280,19 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6323,7 +6319,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6340,109 +6336,109 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1890
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2083
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12172
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -6454,7 +6450,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -6475,13 +6471,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6492,7 +6488,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6504,25 +6500,25 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6600,13 +6596,13 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -6633,13 +6629,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">14645
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6675,7 +6671,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6729,22 +6725,22 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2282
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282
-</t>
-        </is>
-      </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">275
@@ -6759,13 +6755,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187080
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -6792,7 +6788,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -6834,7 +6830,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6870,7 +6866,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -6898,8 +6894,11 @@
 </t>
         </is>
       </c>
-      <c r="U43" s="3" t="n">
-        <v/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
@@ -6915,7 +6914,7 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>531</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6947,7 +6946,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -6983,13 +6982,13 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -7007,26 +7006,24 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -7037,7 +7034,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -7049,27 +7046,24 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v/>
       </c>
       <c r="X44" s="3" t="n">
         <v/>
@@ -7097,43 +7091,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188411
+          <t xml:space="preserve">1682111
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
+          <t xml:space="preserve">8251
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1833
 </t>
         </is>
       </c>
@@ -7145,13 +7138,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28161
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121804
+          <t xml:space="preserve">19104
 </t>
         </is>
       </c>
@@ -7160,76 +7153,79 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101092106191
+          <t xml:space="preserve">100921059
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02041
+          <t xml:space="preserve">0342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168084
+          <t xml:space="preserve">1404
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12572
+          <t xml:space="preserve">2575
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12917
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183179
+          <t xml:space="preserve">13820
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448414
+          <t xml:space="preserve">4840
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">815
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11222
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9247
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7250,7 +7246,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
+          <t xml:space="preserve">3117
 </t>
         </is>
       </c>
@@ -7274,7 +7270,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -7286,7 +7282,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11226
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7298,7 +7294,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -7316,7 +7312,8 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>605</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7333,7 +7330,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -7369,13 +7366,13 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
@@ -697,7 +697,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91124 1
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -727,19 +727,19 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8 8
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
@@ -793,13 +793,13 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -829,7 +829,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>621</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -858,18 +858,24 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
       </c>
       <c r="J5" s="3" t="n">
         <v/>
       </c>
-      <c r="K5" s="3" t="n">
-        <v/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -895,8 +901,11 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
-        <v/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -912,7 +921,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -924,7 +933,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -975,8 +984,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4326
-</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -993,7 +1001,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -1011,19 +1019,19 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -1083,7 +1091,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1144,11 +1152,8 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v/>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1164,13 +1169,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1182,31 +1187,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1236,7 +1241,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
@@ -1252,24 +1257,27 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="3" t="n">
-        <v/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7279
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1290,20 +1298,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297 6
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1314,7 +1321,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -1350,7 +1357,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1398,7 +1405,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1416,18 +1423,21 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1752
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v/>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1452,25 +1462,25 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">8526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1482,7 +1492,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1494,7 +1504,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -1536,13 +1546,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">16173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12319
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -1572,19 +1582,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141024
+          <t xml:space="preserve">4024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1635,21 +1645,27 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1665,7 +1681,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1689,7 +1705,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -1758,7 +1774,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24451
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1776,19 +1792,19 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1800,13 +1816,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1824,68 +1840,66 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25 8
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">587
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247 16
-</t>
-        </is>
-      </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1917,12 +1931,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t xml:space="preserve">383
+</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1946,7 +1961,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1964,7 +1979,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1994,7 +2009,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2042,13 +2057,13 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">11977
 </t>
         </is>
       </c>
@@ -2075,7 +2090,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -2093,7 +2108,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2213,7 +2228,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2234,7 +2249,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -2264,7 +2279,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2274,8 +2289,11 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
-        <v/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2309,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2309,7 +2327,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2339,7 +2357,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -2357,14 +2375,13 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2390,7 +2407,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
+          <t xml:space="preserve">1433
 </t>
         </is>
       </c>
@@ -2402,7 +2419,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
@@ -2420,7 +2437,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2438,7 +2455,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2450,7 +2467,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -2498,13 +2515,13 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -2516,7 +2533,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -2528,7 +2545,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2549,13 +2566,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">19928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192499
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
@@ -2573,54 +2590,50 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v/>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9246
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1058
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4448
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
@@ -2638,13 +2651,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">10425
 </t>
         </is>
       </c>
@@ -2674,8 +2687,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2707,7 +2719,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">3998
 </t>
         </is>
       </c>
@@ -2731,33 +2743,38 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115515
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -2774,7 +2791,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2792,19 +2809,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282240
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -2822,7 +2839,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2861,13 +2878,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -2879,7 +2895,8 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2890,19 +2907,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2913,30 +2930,31 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -2960,7 +2978,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -2978,13 +2996,13 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3017,7 +3035,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t xml:space="preserve">22234
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3058,13 +3077,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -3076,7 +3095,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3100,7 +3119,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -3152,8 +3171,10 @@
 </t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n">
-        <v/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -3172,8 +3193,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9568
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3196,7 +3216,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -3212,12 +3232,16 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
-        <v/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -3240,7 +3264,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3252,13 +3276,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">12415
 </t>
         </is>
       </c>
@@ -3270,13 +3294,13 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">707
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 1
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3288,7 +3312,8 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3380,22 +3405,22 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">867
@@ -3404,7 +3429,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3428,13 +3453,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3458,7 +3483,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8508
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -3485,37 +3510,37 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741
+          <t xml:space="preserve">23746
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2318
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">12475
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -3544,7 +3569,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
@@ -3586,7 +3611,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">2564
 </t>
         </is>
       </c>
@@ -3598,7 +3623,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -3643,13 +3668,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
+          <t xml:space="preserve">1925
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
@@ -3667,7 +3692,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6059
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -3685,13 +3710,13 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4953
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -3727,61 +3752,60 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2952
+          <t xml:space="preserve">28952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3802,7 +3826,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">13985
 </t>
         </is>
       </c>
@@ -3814,25 +3838,25 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -3868,7 +3892,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3886,7 +3910,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3898,7 +3922,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 8
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3910,7 +3934,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3932,8 +3956,11 @@
 </t>
         </is>
       </c>
-      <c r="Y24" s="3" t="n">
-        <v/>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -3958,25 +3985,25 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">23740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
@@ -3994,8 +4021,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4006,7 +4032,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4030,31 +4056,31 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 5
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4066,7 +4092,7 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -4084,7 +4110,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -4096,7 +4122,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -4117,7 +4143,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
@@ -4129,7 +4155,8 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4146,7 +4173,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -4158,7 +4185,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4182,7 +4209,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89 2
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4212,28 +4239,28 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -4242,12 +4269,15 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -4272,13 +4302,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3548
+          <t xml:space="preserve">13544
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4301,13 +4331,13 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4343,7 +4373,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -4379,13 +4409,14 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -4402,8 +4433,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4429,7 +4459,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3893
 </t>
         </is>
       </c>
@@ -4477,7 +4507,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4537,19 +4567,20 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4566,8 +4597,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4593,12 +4623,14 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4609,7 +4641,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4621,7 +4653,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4633,7 +4665,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4651,7 +4683,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4663,7 +4695,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4681,13 +4713,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -4699,7 +4731,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -4744,20 +4776,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118564
+          <t xml:space="preserve">18564
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4768,13 +4799,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
@@ -4798,7 +4829,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9296
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4810,7 +4841,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
@@ -4828,7 +4859,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -4852,7 +4883,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4870,12 +4901,14 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>439</t>
+          <t xml:space="preserve">3998
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4901,23 +4934,25 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">371
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>096</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4935,18 +4970,21 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4992,13 +5030,13 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -5010,7 +5048,7 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5022,18 +5060,21 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -5052,13 +5093,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4128
+          <t xml:space="preserve">13528
 </t>
         </is>
       </c>
@@ -5070,13 +5111,13 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1669
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
@@ -5088,7 +5129,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5100,7 +5141,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5118,7 +5159,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -5130,8 +5171,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5160,19 +5200,19 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
@@ -5184,13 +5224,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5211,12 +5251,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t xml:space="preserve">3979
+</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
@@ -5251,12 +5292,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5298,7 +5340,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5310,43 +5352,43 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17276
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5367,7 +5409,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
+          <t xml:space="preserve">13624
 </t>
         </is>
       </c>
@@ -5397,7 +5439,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5409,13 +5451,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5481,7 +5523,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -5499,7 +5541,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -5556,7 +5598,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5580,7 +5622,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5592,7 +5634,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5634,13 +5676,13 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5691,13 +5733,14 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5714,7 +5757,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0 1
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5726,13 +5769,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5750,7 +5793,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5798,7 +5841,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5810,7 +5853,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5820,8 +5863,10 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n">
-        <v/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5840,7 +5885,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116835
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
@@ -5852,19 +5897,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
@@ -5888,7 +5933,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
@@ -5906,7 +5951,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
@@ -5936,7 +5981,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12560
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -5999,7 +6044,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
+          <t xml:space="preserve">23267
 </t>
         </is>
       </c>
@@ -6017,7 +6062,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
@@ -6041,7 +6086,8 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -6058,13 +6104,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 3
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -6094,7 +6140,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6106,7 +6152,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -6118,7 +6164,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 1
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6136,7 +6182,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6157,7 +6203,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">14008
 </t>
         </is>
       </c>
@@ -6181,18 +6227,21 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -6220,7 +6269,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6232,13 +6281,13 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6250,7 +6299,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6274,7 +6323,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -6319,30 +6368,31 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">2841
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
@@ -6378,7 +6428,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -6426,13 +6476,13 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2083
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6444,13 +6494,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
@@ -6471,24 +6521,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
+          <t xml:space="preserve">2448
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -6506,7 +6557,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6596,7 +6647,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6608,7 +6659,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6629,7 +6680,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14645
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -6653,7 +6704,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6683,7 +6734,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6707,7 +6758,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6725,13 +6776,13 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1500
 </t>
         </is>
       </c>
@@ -6749,25 +6800,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -6788,7 +6839,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
@@ -6800,7 +6851,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -6812,7 +6863,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6854,19 +6905,19 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6884,7 +6935,7 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -6896,7 +6947,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6914,12 +6965,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -6964,7 +7015,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -6988,7 +7039,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -7000,30 +7051,31 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2041
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -7046,24 +7098,27 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
       </c>
       <c r="X44" s="3" t="n">
         <v/>
@@ -7091,42 +7146,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682111
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8251
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t xml:space="preserve">1056
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -7138,88 +7193,87 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19104
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1092
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12181
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1575
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1385
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4240
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11215
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1455
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="n">
         <v/>
       </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100921059
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0342
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2575
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13820
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4840
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">483904
 </t>
         </is>
       </c>
@@ -7258,7 +7312,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7270,13 +7324,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">11676
 </t>
         </is>
       </c>
@@ -7292,11 +7346,8 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7318,7 +7369,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -7330,7 +7381,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -7366,13 +7417,13 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -679,128 +679,107 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X4" s="3" t="n">
@@ -834,38 +813,32 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
@@ -873,98 +846,82 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -989,140 +946,117 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1142,14 +1076,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -1157,128 +1089,107 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1298,14 +1209,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1315,128 +1224,107 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1456,146 +1344,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1615,146 +1479,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1774,104 +1614,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1881,20 +1704,17 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1904,14 +1724,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1931,146 +1749,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
+          <t>383</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2090,146 +1884,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2249,134 +2019,112 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2386,8 +2134,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2407,146 +2154,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2566,26 +2289,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2595,20 +2314,17 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
@@ -2621,68 +2337,57 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2692,14 +2397,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2719,146 +2422,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115515
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2883,38 +2562,32 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2924,98 +2597,82 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3035,140 +2692,117 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3198,140 +2832,117 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12415
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3351,146 +2962,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3510,32 +3097,27 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12475
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3545,110 +3127,92 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3668,110 +3232,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3781,32 +3327,27 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3826,146 +3367,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3985,38 +3502,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4026,104 +3537,87 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4143,146 +3637,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4302,8 +3772,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4313,122 +3782,102 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4438,8 +3887,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4459,140 +3907,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4617,146 +4042,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4776,14 +4177,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4793,128 +4192,107 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4934,146 +4312,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5093,80 +4447,67 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13528
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5176,62 +4517,52 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5251,38 +4582,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5292,104 +4617,87 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5409,146 +4717,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5568,146 +4852,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5727,140 +4987,117 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5885,146 +5122,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6044,146 +5257,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6203,146 +5392,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6362,146 +5527,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6521,146 +5662,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6680,146 +5797,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6839,128 +5932,107 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6970,14 +6042,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6997,74 +6067,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2041
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -7074,50 +6132,42 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X44" s="3" t="n">
@@ -7151,68 +6201,57 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -7222,50 +6261,42 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="3" t="n">
@@ -7273,14 +6304,12 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7300,131 +6329,112 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3392,34 +3392,34 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>193</t>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5662,17 +5662,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/209/209_196810_SF.JPG_pre_QA_QC.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>649</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6339,49 +6339,49 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>202</t>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
